--- a/UK_CoP_TitleLists/BMJ_Hybrid_scifreeimport.xlsx
+++ b/UK_CoP_TitleLists/BMJ_Hybrid_scifreeimport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d4b02a2393526de/Documents/CoP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{F0C1A7F3-2CF2-48F2-B69D-228FBB497B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DF03860-0E04-446A-9A7A-0C7D467F7D53}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{F0C1A7F3-2CF2-48F2-B69D-228FBB497B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B448EA4-0139-4E95-9FBD-A185B720E95F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{BE44926E-75A4-4EDC-A463-0127E7F3749D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="202">
   <si>
     <t>Journal Title</t>
   </si>
@@ -650,12 +650,18 @@
   <si>
     <t>Archives of Disease in Childhood: Fetal &amp; Neonatal</t>
   </si>
+  <si>
+    <t>CC BY, CC-BY-NC</t>
+  </si>
+  <si>
+    <t>Note: Updated licences to include CC-BY-NC where applicable</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -709,6 +715,14 @@
       <color rgb="FF333333"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -956,10 +970,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -990,9 +1005,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1010,426 +1022,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="35">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1576,6 +1178,396 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <top style="thin">
           <color theme="9" tint="-0.499984740745262"/>
@@ -1597,6 +1589,31 @@
           <color theme="9" tint="-0.499984740745262"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -2082,33 +2099,33 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50DE42A8-741C-4C2A-82B7-4C9C79D7B512}" name="Table14" displayName="Table14" ref="A4:J7" totalsRowShown="0" headerRowDxfId="21" dataDxfId="0" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50DE42A8-741C-4C2A-82B7-4C9C79D7B512}" name="Table14" displayName="Table14" ref="A4:J7" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="A4:J7" xr:uid="{50DE42A8-741C-4C2A-82B7-4C9C79D7B512}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{1B9A1423-FE7E-41D7-B053-6BF091F459D2}" name="Journal Title" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{B625EB42-AF86-4F71-BC2F-65D99997CD50}" name="Imprint" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{559DDF72-C949-47E4-8DA4-297063A6725C}" name="Print ISSN" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{2C5C0518-FAE9-4E34-9C5C-031EDE4262BA}" name="Electronic ISSN" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{D5474278-5905-4A79-9DFE-DE4AB9980E12}" name="Journal URL" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{3D861C40-F9D7-4168-ACD1-389CE9995730}" name="Publishing Model" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{156C7878-43A4-40BA-84D1-0BD24E590EEE}" name="License Options" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{4C684C0B-6FA6-4E1F-BC47-B228FA209770}" name="Subject Areas" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{96CDE76D-4B76-48A4-98FB-70E2CCC4CFC8}" name="Change Type (See Terms)" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{43B192BA-2299-4882-A245-9C663CF7CF9B}" name="Change Note" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{1B9A1423-FE7E-41D7-B053-6BF091F459D2}" name="Journal Title" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{B625EB42-AF86-4F71-BC2F-65D99997CD50}" name="Imprint" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{559DDF72-C949-47E4-8DA4-297063A6725C}" name="Print ISSN" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{2C5C0518-FAE9-4E34-9C5C-031EDE4262BA}" name="Electronic ISSN" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{D5474278-5905-4A79-9DFE-DE4AB9980E12}" name="Journal URL" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{3D861C40-F9D7-4168-ACD1-389CE9995730}" name="Publishing Model" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{156C7878-43A4-40BA-84D1-0BD24E590EEE}" name="License Options" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{4C684C0B-6FA6-4E1F-BC47-B228FA209770}" name="Subject Areas" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{96CDE76D-4B76-48A4-98FB-70E2CCC4CFC8}" name="Change Type (See Terms)" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{43B192BA-2299-4882-A245-9C663CF7CF9B}" name="Change Note" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{98A0D124-AED4-4DBE-8354-EE3315983F60}" name="Table25" displayName="Table25" ref="A1:B11" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{98A0D124-AED4-4DBE-8354-EE3315983F60}" name="Table25" displayName="Table25" ref="A1:B11" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="A1:B11" xr:uid="{98A0D124-AED4-4DBE-8354-EE3315983F60}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B11">
     <sortCondition ref="A1:A11"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E088FFDE-8F3A-4B84-9B24-F82FF70FAEA5}" name="Term" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{3BB7484B-180C-438A-8248-E8FEA43CCABB}" name="Description" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{E088FFDE-8F3A-4B84-9B24-F82FF70FAEA5}" name="Term" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{3BB7484B-180C-438A-8248-E8FEA43CCABB}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2491,7 +2508,7 @@
         <v>31</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H2" s="18"/>
     </row>
@@ -2508,14 +2525,14 @@
       <c r="D3" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="35" t="s">
         <v>138</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>31</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H3" s="18"/>
     </row>
@@ -2532,14 +2549,14 @@
       <c r="D4" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="35" t="s">
         <v>139</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>31</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H4" s="18"/>
     </row>
@@ -2556,14 +2573,14 @@
       <c r="D5" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="35" t="s">
         <v>140</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H5" s="18"/>
     </row>
@@ -2578,14 +2595,14 @@
       <c r="D6" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="35" t="s">
         <v>175</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>31</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H6" s="18"/>
       <c r="J6" s="10"/>
@@ -2603,14 +2620,14 @@
       <c r="D7" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="35" t="s">
         <v>141</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>31</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H7" s="18"/>
     </row>
@@ -2625,14 +2642,14 @@
       <c r="D8" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="35" t="s">
         <v>142</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H8" s="18"/>
     </row>
@@ -2656,7 +2673,7 @@
         <v>31</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H9" s="18"/>
     </row>
@@ -2680,7 +2697,7 @@
         <v>31</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H10" s="18"/>
     </row>
@@ -2704,7 +2721,7 @@
         <v>31</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H11" s="18"/>
     </row>
@@ -2728,7 +2745,7 @@
         <v>31</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H12" s="18"/>
     </row>
@@ -2752,7 +2769,7 @@
         <v>31</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H13" s="18"/>
     </row>
@@ -2776,7 +2793,7 @@
         <v>31</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H14" s="18"/>
     </row>
@@ -2798,7 +2815,7 @@
         <v>31</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H15" s="18"/>
     </row>
@@ -2822,7 +2839,7 @@
         <v>31</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H16" s="18"/>
     </row>
@@ -2846,7 +2863,7 @@
         <v>31</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H17" s="18"/>
     </row>
@@ -2870,7 +2887,7 @@
         <v>31</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H18" s="18"/>
     </row>
@@ -2894,7 +2911,7 @@
         <v>31</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H19" s="18"/>
     </row>
@@ -2918,7 +2935,7 @@
         <v>31</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H20" s="18"/>
     </row>
@@ -2942,7 +2959,7 @@
         <v>31</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H21" s="18"/>
     </row>
@@ -2966,7 +2983,7 @@
         <v>31</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H22" s="18"/>
     </row>
@@ -2990,7 +3007,7 @@
         <v>31</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H23" s="18"/>
     </row>
@@ -3014,7 +3031,7 @@
         <v>31</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H24" s="18"/>
     </row>
@@ -3038,7 +3055,7 @@
         <v>31</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H25" s="18"/>
     </row>
@@ -3062,7 +3079,7 @@
         <v>31</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H26" s="18"/>
     </row>
@@ -3086,7 +3103,7 @@
         <v>31</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H27" s="18"/>
     </row>
@@ -3110,7 +3127,7 @@
         <v>31</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H28" s="18"/>
     </row>
@@ -3134,7 +3151,7 @@
         <v>31</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H29" s="18"/>
     </row>
@@ -3156,7 +3173,7 @@
         <v>31</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H30" s="18"/>
     </row>
@@ -3180,7 +3197,7 @@
         <v>31</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H31" s="18"/>
     </row>
@@ -3204,7 +3221,7 @@
         <v>31</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H32" s="18"/>
     </row>
@@ -3228,7 +3245,7 @@
         <v>31</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H33" s="18"/>
     </row>
@@ -3252,7 +3269,7 @@
         <v>31</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H34" s="18"/>
     </row>
@@ -3276,7 +3293,7 @@
         <v>31</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H35" s="18"/>
     </row>
@@ -3300,7 +3317,7 @@
         <v>31</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="H36" s="18"/>
     </row>
@@ -3323,8 +3340,8 @@
       <c r="F37" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G37" s="26" t="s">
-        <v>173</v>
+      <c r="G37" s="15" t="s">
+        <v>200</v>
       </c>
       <c r="H37" s="27"/>
     </row>
@@ -3376,17 +3393,25 @@
       <c r="H50" s="13"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{D03ADE44-2817-4BC3-B1CF-FFB52FEAF855}"/>
+    <hyperlink ref="E4" r:id="rId2" xr:uid="{3C204190-8FAD-4393-9E8F-CFC44E2FA325}"/>
+    <hyperlink ref="E5" r:id="rId3" xr:uid="{91EB2C87-54DB-4539-B602-A37797834A5D}"/>
+    <hyperlink ref="E6" r:id="rId4" xr:uid="{4EC41E62-0E7D-4359-834D-9ECBF50ADC17}"/>
+    <hyperlink ref="E7" r:id="rId5" xr:uid="{5C4CEBDF-80BD-4BB4-917F-EC522C1F4934}"/>
+    <hyperlink ref="E8" r:id="rId6" xr:uid="{3579D73E-7F6C-4E37-9DEE-981F5B59ED60}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FC2B06-4BD0-4FEC-9578-53390E6CC2F6}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.08984375" style="9" customWidth="1"/>
@@ -3403,60 +3428,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
     </row>
     <row r="4" spans="1:10" ht="31" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="29" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3479,7 +3504,7 @@
       <c r="F5" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="32" t="s">
         <v>173</v>
       </c>
       <c r="H5" s="15"/>
@@ -3491,56 +3516,56 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33" t="s">
+      <c r="B6" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="F6" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="33" t="s">
+      <c r="F6" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33" t="s">
+      <c r="H6" s="32"/>
+      <c r="I6" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="J6" s="33" t="s">
+      <c r="J6" s="32" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="32"/>
+      <c r="C7" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="33" t="s">
+      <c r="F7" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33" t="s">
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32" t="s">
         <v>182</v>
       </c>
     </row>
@@ -3548,7 +3573,7 @@
       <c r="A8" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="32" t="s">
         <v>172</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -3563,10 +3588,10 @@
       <c r="F8" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="H8" s="33"/>
+      <c r="H8" s="32"/>
       <c r="I8" s="15" t="s">
         <v>188</v>
       </c>
@@ -3578,7 +3603,7 @@
       <c r="A9" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="32" t="s">
         <v>172</v>
       </c>
       <c r="C9" s="15" t="s">
@@ -3593,10 +3618,10 @@
       <c r="F9" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="H9" s="33"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="15" t="s">
         <v>191</v>
       </c>
@@ -3605,34 +3630,34 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="14" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="31" t="s">
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="F10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="34" t="s">
+      <c r="F10" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="H10" s="32"/>
-      <c r="I10" s="35" t="s">
+      <c r="H10" s="31"/>
+      <c r="I10" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="J10" s="32"/>
+      <c r="J10" s="31"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="32" t="s">
         <v>172</v>
       </c>
       <c r="C11" s="15" t="s">
@@ -3647,15 +3672,20 @@
       <c r="F11" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="H11" s="33"/>
+      <c r="H11" s="32"/>
       <c r="I11" s="15" t="s">
         <v>191</v>
       </c>
       <c r="J11" s="15" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
